--- a/TDD_examples/CASE_2_ENEA_HTS_CICC/conductor_diagnostic.xlsx
+++ b/TDD_examples/CASE_2_ENEA_HTS_CICC/conductor_diagnostic.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spatial_distribution" sheetId="1" r:id="R81f1e985c86640c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time_evolution" sheetId="2" r:id="Rc7e3c278552c4137"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spatial_distribution" sheetId="1" r:id="R62467d35da494132"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Time_evolution" sheetId="2" r:id="R8a7f1dfe1ff84cd0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,7 +345,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>time to plot spatial dustribution of the solution </x:v>
+        <x:v>Time at which the spatial distribution of the solution is plotted.</x:v>
       </x:c>
       <x:c r="E4" s="5" t="n">
         <x:v>14</x:v>
@@ -394,7 +394,7 @@
       <x:c r="D7"/>
       <x:c r="E7" s="5" t="n">
         <x:f t="shared" ref="E7:E26" si="0">E6+0.05</x:f>
-        <x:v>15.1</x:v>
+        <x:v>15.100000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="13.899999618530273" customHeight="1">
